--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1358,7 +1358,7 @@
       <c r="I12" s="43" t="n"/>
       <c r="J12" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1 cerrado en horas: 11 tareas y 43 h estimadas, con 43 h reales registradas (Luis 15, Rodrigo 14, Nicolás 14). Pendiente la Sprint Review y el documento Validando Sprint 1.</t>
+          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; falta la aceptación del Product Owner (columna A/R) en la Sprint Review.</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       <c r="I15" s="43" t="n"/>
       <c r="J15" s="43" t="inlineStr">
         <is>
-          <t>Plantilla ya lista (Plantilla_Resumen_Reunion_Retrospectiva.docx), pendiente la primera sesión al cerrar el Sprint 1.</t>
+          <t>Plantilla lista con la identificación del Sprint 1; la completan Luis Méndez y Nicolás Silva en la reunión retrospectiva (el Product Owner no asiste).</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -669,6 +669,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="23">
       <c r="A4" s="26" t="inlineStr">
         <is>
@@ -928,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A4:J17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="22" min="1" max="2"/>
@@ -942,6 +943,9 @@
     <col width="35" customWidth="1" style="22" min="10" max="10"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="23">
       <c r="A4" s="39" t="inlineStr">
         <is>
@@ -1310,7 +1314,7 @@
       <c r="I11" s="43" t="n"/>
       <c r="J11" s="43" t="inlineStr">
         <is>
-          <t>Cubierto por PMOInformatica_Plantilla_de_Product_Backlog.xlsx y la priorización por 100 puntos en Artefactos Fase Inicio.</t>
+          <t>Cubierto por PMOInformatica_Plantilla_de_Product_Backlog.xlsx y la priorización por 100 puntos en Artefactos Fase Inicio. Al 21-09-2026 el Product Backlog tiene 19 historias (FS-HU-15 a FS-HU-19 agregadas en el Sprint 2).</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1362,7 @@
       <c r="I12" s="43" t="n"/>
       <c r="J12" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; falta la aceptación del Product Owner (columna A/R) en la Sprint Review.</t>
+          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; falta la aceptación del Product Owner (columna A/R) en la Sprint Review. Sprint 2: borrador con 23 tareas en 'Sprint 2/PMOInformatica_Plantilla_de_Sprint_Backlog.xlsx'; horas estimadas y responsables pendientes de la planificación del equipo.</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1550,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 7 casos del Sprint 1 ejecutados y aprobados (CP-001 a CP-007). Registro de Defectos con 2 defectos corregidos. Evidencias en Fase 2/Evidencias Sprint 1.</t>
+          <t>Planilla de Casos de Prueba: 7 casos del Sprint 1 ejecutados y aprobados (CP-001 a CP-007). Registro de Defectos con 2 defectos corregidos. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint 1/Capturas del sistema.</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A4:G28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="22" min="1" max="1"/>
@@ -1625,6 +1629,9 @@
     <col width="35" customWidth="1" style="22" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="23">
       <c r="A4" s="39" t="inlineStr">
         <is>
@@ -1687,7 +1694,7 @@
       <c r="F5" s="43" t="n"/>
       <c r="G5" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.0: Vista Física (Ilustración 5) y Vista Lógica por capas.</t>
+          <t>DAS v1.9: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1723,7 @@
       <c r="F6" s="43" t="n"/>
       <c r="G6" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.0, Vista Física: tabla de nodos (Nginx, Node.js/Express, MySQL 8, Google Maps, API de Claude).</t>
+          <t>DAS v1.9, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, Google Maps, API de Claude, Google Identity Services y servidor SMTP).</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1752,7 @@
       <c r="F7" s="43" t="n"/>
       <c r="G7" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.0, Vista Física: tabla de comunicación (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx).</t>
+          <t>DAS v1.9, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1810,7 @@
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.0, Vista Lógica &gt; Diccionario de datos: 8 tablas con tipos, PK, FK, restricciones e índices.</t>
+          <t>DAS v1.9, Vista Lógica &gt; Diccionario de datos: 12 tablas con tipos, PK, FK, restricciones e índices.</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1839,7 @@
       <c r="F10" s="43" t="n"/>
       <c r="G10" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.0, Ilustración 1 y tabla CU-01 a CU-07.</t>
+          <t>DAS v1.9, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend») y tabla de casos de uso.</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1868,7 @@
       <c r="F11" s="43" t="n"/>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.0, Vista de Procesos: secuencia de registro de comida (Ilustración 3) y flujo de autenticación del Sprint 1.</t>
+          <t>DAS v1.9, Vista de Procesos: secuencias del registro de comida (Ilustración 5), del asistente de perfil (Ilustración 6), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8).</t>
         </is>
       </c>
     </row>
@@ -1913,13 +1920,13 @@
       <c r="D13" s="43" t="n"/>
       <c r="E13" s="44" t="inlineStr">
         <is>
-          <t>En Desarrollo</t>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="inlineStr">
         <is>
-          <t>Diagrama de clases en el DAS (Ilustración 2); debe alinearse con el modelo de datos (Usuario-Conversación 1..N, faltan Rol y PerfilUsuario).</t>
+          <t>DAS v1.9, Ilustración 2: diagrama de clases del dominio (12 clases alineadas con el modelo de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -669,7 +669,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="23">
       <c r="A4" s="26" t="inlineStr">
         <is>
@@ -929,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A4:J17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="22" min="1" max="2"/>
@@ -943,9 +942,6 @@
     <col width="35" customWidth="1" style="22" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="23">
       <c r="A4" s="39" t="inlineStr">
         <is>
@@ -1410,7 +1406,7 @@
       <c r="I13" s="43" t="n"/>
       <c r="J13" s="43" t="inlineStr">
         <is>
-          <t>Documento Fase 2/Definition_of_Done.docx (15 criterios por historia y 5 por sprint). Aprobado por el Product Owner el 20-09-2026; pendientes las aprobaciones de Luis Méndez y Nicolás Silva.</t>
+          <t>Documento FASE 2/Evidencias Proyecto/Evidencias de documentación/Definition_of_Done.docx (v1.5: 15 criterios por historia y 5 por sprint). Aprobado por Rodrigo Cárcamo Rojas (Product Owner) el 20-09-2026 y por Luis Méndez (Scrum Master) el 22-09-2026 mediante el pull request #1 revisado y fusionado en GitHub; pendiente la aprobación de Nicolás Silva.</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A4:G28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="22" min="1" max="1"/>
@@ -1629,9 +1625,6 @@
     <col width="35" customWidth="1" style="22" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="23">
       <c r="A4" s="39" t="inlineStr">
         <is>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1310,7 +1310,7 @@
       <c r="I11" s="43" t="n"/>
       <c r="J11" s="43" t="inlineStr">
         <is>
-          <t>Cubierto por PMOInformatica_Plantilla_de_Product_Backlog.xlsx y la priorización por 100 puntos en Artefactos Fase Inicio. Al 21-09-2026 el Product Backlog tiene 19 historias (FS-HU-15 a FS-HU-19 agregadas en el Sprint 2).</t>
+          <t>Cubierto por PMOInformatica_Plantilla_de_Product_Backlog.xlsx y la priorización por 100 puntos en Artefactos Fase Inicio. Al 23-09-2026 el Product Backlog tiene 20 historias (FS-HU-15 a FS-HU-20 agregadas en el Sprint 2).</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A4:G28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="22" min="1" max="1"/>
@@ -1625,6 +1625,9 @@
     <col width="35" customWidth="1" style="22" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="23">
       <c r="A4" s="39" t="inlineStr">
         <is>
@@ -1687,7 +1690,7 @@
       <c r="F5" s="43" t="n"/>
       <c r="G5" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.9: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
+          <t>DAS v1.11: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1719,7 @@
       <c r="F6" s="43" t="n"/>
       <c r="G6" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.9, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, Google Maps, API de Claude, Google Identity Services y servidor SMTP).</t>
+          <t>DAS v1.11, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, Google Maps, API de Claude, Google Identity Services y servidor SMTP).</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1748,7 @@
       <c r="F7" s="43" t="n"/>
       <c r="G7" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.9, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
+          <t>DAS v1.11, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1806,7 @@
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.9, Vista Lógica &gt; Diccionario de datos: 12 tablas con tipos, PK, FK, restricciones e índices.</t>
+          <t>DAS v1.11, Vista Lógica &gt; Diccionario de datos: 12 tablas con tipos, PK, FK, restricciones e índices.</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1835,7 @@
       <c r="F10" s="43" t="n"/>
       <c r="G10" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.9, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend») y tabla de casos de uso.</t>
+          <t>DAS v1.11, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend») y tabla de casos de uso.</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1864,7 @@
       <c r="F11" s="43" t="n"/>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.9, Vista de Procesos: secuencias del registro de comida (Ilustración 5), del asistente de perfil (Ilustración 6), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8).</t>
+          <t>DAS v1.11, Vista de Procesos: secuencias del registro de comida (Ilustración 5), del asistente de perfil (Ilustración 6), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8).</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1922,7 @@
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.9, Ilustración 2: diagrama de clases del dominio (12 clases alineadas con el modelo de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
+          <t>DAS v1.11, Ilustración 2: diagrama de clases del dominio (12 clases alineadas con el modelo de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1406,7 +1406,7 @@
       <c r="I13" s="43" t="n"/>
       <c r="J13" s="43" t="inlineStr">
         <is>
-          <t>Documento FASE 2/Evidencias Proyecto/Evidencias de documentación/Definition_of_Done.docx (v1.5: 15 criterios por historia y 5 por sprint). Aprobado por Rodrigo Cárcamo Rojas (Product Owner) el 20-09-2026 y por Luis Méndez (Scrum Master) el 22-09-2026 mediante el pull request #1 revisado y fusionado en GitHub; pendiente la aprobación de Nicolás Silva.</t>
+          <t>Documento FASE 2/Evidencias Proyecto/Evidencias de documentación/Definition_of_Done.docx (v1.6: 15 criterios por historia y 5 por sprint). Aprobado por Rodrigo Cárcamo Rojas (Product Owner) el 20-09-2026, por Luis Méndez (Scrum Master) el 22-09-2026 mediante el pull request #1 y por Nicolás Silva (Desarrollador) el 22-09-2026 mediante el pull request #5, ambos revisados y fusionados en GitHub.</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A4:G28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="22" min="1" max="1"/>
@@ -1625,9 +1625,6 @@
     <col width="35" customWidth="1" style="22" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="23">
       <c r="A4" s="39" t="inlineStr">
         <is>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1358,7 +1358,7 @@
       <c r="I12" s="43" t="n"/>
       <c r="J12" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; falta la aceptación del Product Owner (columna A/R) en la Sprint Review. Sprint 2: borrador con 23 tareas en 'Sprint 2/PMOInformatica_Plantilla_de_Sprint_Backlog.xlsx'; horas estimadas y responsables pendientes de la planificación del equipo.</t>
+          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; el Product Owner aceptó FS-HU-01 y FS-HU-02 el 24-09-2026 (columna A/R, con observaciones) y la retrospectiva quedó registrada el 24-09-2026; Luis Méndez aprobó la revisión posterior del código (PR #6) el 24-09-2026; Sprint 1 cerrado. Sprint 2: borrador con 23 tareas en 'Sprint 2/PMOInformatica_Plantilla_de_Sprint_Backlog.xlsx'; horas estimadas y responsables pendientes de la planificación del equipo.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1310,7 +1310,7 @@
       <c r="I11" s="43" t="n"/>
       <c r="J11" s="43" t="inlineStr">
         <is>
-          <t>Cubierto por PMOInformatica_Plantilla_de_Product_Backlog.xlsx y la priorización por 100 puntos en Artefactos Fase Inicio. Al 23-09-2026 el Product Backlog tiene 20 historias (FS-HU-15 a FS-HU-20 agregadas en el Sprint 2).</t>
+          <t>Cubierto por PMOInformatica_Plantilla_de_Product_Backlog.xlsx y la priorización por 100 puntos en Artefactos Fase Inicio. Al 23-09-2026 el Product Backlog tiene 20 historias (FS-HU-15 a FS-HU-20 agregadas en el Sprint 2). Al 24-09-2026 FS-HU-16 (acceso con Google) pasó a En Proceso: el ID de cliente OAuth quedó creado con la cuenta fitsearchoficial@gmail.com y la funcionalidad está implementada. El 24-09-2026 el Product Owner cambió el flujo de registro: el tipo de cuenta (rol) se elige en el asistente de perfil y no al registrarse, lo que ajustó FS-HU-02, FS-HU-16 y FS-HU-17.</t>
         </is>
       </c>
     </row>
